--- a/administrative_forms/026_office_ergonomics_assessment_form--administrative_forms.xlsx
+++ b/administrative_forms/026_office_ergonomics_assessment_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'1.5_hours'}</t>
+          <t>1.5_hours</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '1.5 hours'}</t>
+          <t>1.5 hours</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'standing_desk'}</t>
+          <t>standing_desk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Standing Desk'}</t>
+          <t>Standing Desk</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'proper_posture'}</t>
+          <t>proper_posture</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Proper Posture'}</t>
+          <t>Proper Posture</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'open_office'}</t>
+          <t>open_office</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Open Office'}</t>
+          <t>Open Office</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'adjusted'}</t>
+          <t>adjusted</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Adjusted'}</t>
+          <t>Adjusted</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'standing_desk'}</t>
+          <t>standing_desk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Standing Desk'}</t>
+          <t>Standing Desk</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'standing_desk'}</t>
+          <t>standing_desk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Standing Desk'}</t>
+          <t>Standing Desk</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'standing_desk'}</t>
+          <t>standing_desk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Standing Desk'}</t>
+          <t>Standing Desk</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'standing_desk'}</t>
+          <t>standing_desk</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Standing Desk'}</t>
+          <t>Standing Desk</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'improved_posture'}</t>
+          <t>improved_posture</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Improved Posture'}</t>
+          <t>Improved Posture</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'improved_posture'}</t>
+          <t>improved_posture</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Improved Posture'}</t>
+          <t>Improved Posture</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'improved_health'}</t>
+          <t>improved_health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Improved Health'}</t>
+          <t>Improved Health</t>
         </is>
       </c>
     </row>
